--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios168.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios168.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.3803056581883</v>
+        <v>25.52165756798313</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.32517641287921</v>
+        <v>29.38387118486623</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.48454647214405</v>
+        <v>29.4268945511024</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.3994796512275</v>
+        <v>26.71015322597733</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.03683085226639</v>
+        <v>31.90327033877592</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23.07331956882493</v>
+        <v>17.22450875083157</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31.09082872510506</v>
+        <v>25.08480830583128</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.32611151831048</v>
+        <v>29.65143004118822</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23.58368386798633</v>
+        <v>29.66144519149528</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.69617755374897</v>
+        <v>26.28856753705578</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31.19021607451964</v>
+        <v>32.01999030736107</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22.69574399628068</v>
+        <v>17.13186484374422</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31.03932935820254</v>
+        <v>25.53659596134007</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27.91779248111713</v>
+        <v>29.56151625091952</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23.56498616638665</v>
+        <v>29.82270251973921</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.44297527790327</v>
+        <v>26.74411212859321</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30.86890268045494</v>
+        <v>32.16622267263315</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>22.7385960698496</v>
+        <v>17.13117351291829</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.08023182609192</v>
+        <v>25.66329438406707</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27.93595711358786</v>
+        <v>29.42187477489548</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23.22263321325666</v>
+        <v>29.47798607026893</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.58354240160196</v>
+        <v>26.59429358720882</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31.20209538559169</v>
+        <v>32.05499077583924</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>22.42258401965566</v>
+        <v>17.33188781212301</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30.7983987921562</v>
+        <v>25.573210997774</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27.41875714917942</v>
+        <v>29.28698439238419</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>23.35080279194507</v>
+        <v>29.4443278254637</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.73541178725175</v>
+        <v>26.87318216998078</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31.10710675128573</v>
+        <v>31.87028213967497</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22.71459333482472</v>
+        <v>16.96422312812221</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31.19020544561157</v>
+        <v>25.76957151031728</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28.08213000512844</v>
+        <v>29.4403418554765</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>23.92401038331162</v>
+        <v>29.90498663723931</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29.10781283348804</v>
+        <v>27.10947223037629</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31.33693166665713</v>
+        <v>31.92593680308753</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>22.80076555083588</v>
+        <v>16.93609215199885</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>31.10547889134595</v>
+        <v>25.35736709499716</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27.49649843312154</v>
+        <v>29.29956250865406</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>23.56583776799872</v>
+        <v>29.65804627634915</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>29.72339730809064</v>
+        <v>26.71831981791384</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30.97674775532105</v>
+        <v>32.2778007836954</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>22.63668545999978</v>
+        <v>17.32688254997114</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30.91793911605993</v>
+        <v>25.63544745846339</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>27.67112090786943</v>
+        <v>29.76695898963087</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>23.67915228337735</v>
+        <v>29.03980672382814</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>29.93172277299989</v>
+        <v>26.89208652087522</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>31.0031570811989</v>
+        <v>32.71586025416065</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>22.9062627677652</v>
+        <v>16.57372725114038</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>33.43393796279796</v>
+        <v>25.34379021237217</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>29.15732630215321</v>
+        <v>31.5683578239161</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>28.82932441388234</v>
+        <v>24.91415597807234</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>31.82690705700523</v>
+        <v>22.96834626433409</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>30.12312923817066</v>
+        <v>28.38046755988312</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>26.92297720273652</v>
+        <v>22.57238005821834</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>33.05108908982986</v>
+        <v>25.07684074056399</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>29.03598581949072</v>
+        <v>31.32043168733076</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>29.03147347883931</v>
+        <v>25.16403141385614</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>31.81117020481612</v>
+        <v>22.98476131801954</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>30.13112489166369</v>
+        <v>27.79540049890607</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>27.01151013012628</v>
+        <v>22.33369603119942</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>33.34816612785913</v>
+        <v>25.88057586345958</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>28.79895648543685</v>
+        <v>31.95980121360029</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>28.76669374161551</v>
+        <v>25.41669059758798</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>31.78199806443278</v>
+        <v>22.45306482073803</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>30.0467570032464</v>
+        <v>27.70607176242047</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>27.1141283665364</v>
+        <v>22.41546590202501</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>33.33314867716417</v>
+        <v>24.91828172573777</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>28.70745950571523</v>
+        <v>32.12477054632016</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>29.30580664339732</v>
+        <v>25.4820687326714</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>32.36474222540858</v>
+        <v>22.66423009812685</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>29.79761797145785</v>
+        <v>28.40117542917169</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>27.25509756070521</v>
+        <v>22.3977857411417</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>32.89973701020057</v>
+        <v>25.82202716262642</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>28.72724134763254</v>
+        <v>31.6644929439812</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>29.42392165759093</v>
+        <v>25.27247375775722</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>31.79927126647312</v>
+        <v>23.10478192184185</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30.17397082231687</v>
+        <v>28.2599046214408</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>27.38354770563201</v>
+        <v>22.51313569533058</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>32.78384282225824</v>
+        <v>25.13474535917969</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>28.57493533690705</v>
+        <v>31.78130731271219</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>28.49840273563637</v>
+        <v>24.92260160347242</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>31.6147770472416</v>
+        <v>22.82046757494239</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>29.20878591671804</v>
+        <v>27.59386692446979</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>27.38443590435548</v>
+        <v>21.9998431417018</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>33.79545373911774</v>
+        <v>25.18296331280413</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>28.86398968704918</v>
+        <v>32.01786143282236</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>28.43775441242199</v>
+        <v>25.36032314940595</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>31.69234966983474</v>
+        <v>22.76713831186366</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>29.92770208179109</v>
+        <v>28.39087100759761</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>26.95896228920342</v>
+        <v>22.27127558626301</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>33.40005450218838</v>
+        <v>24.68754708604166</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>29.05491387428057</v>
+        <v>30.92879196134141</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>28.51299047389066</v>
+        <v>24.83088383476776</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>32.12866033057784</v>
+        <v>22.97187718862755</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.52471286644804</v>
+        <v>27.72626991743568</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>27.75429572661825</v>
+        <v>22.50198707635457</v>
       </c>
     </row>
     <row r="98">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>32.24729657206372</v>
+        <v>28.98820977878366</v>
       </c>
     </row>
     <row r="99">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>25.7361379658605</v>
+        <v>26.66529023268927</v>
       </c>
     </row>
     <row r="100">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>26.95105229456348</v>
+        <v>26.82558280571372</v>
       </c>
     </row>
     <row r="101">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>28.25111309071987</v>
+        <v>27.95535640600297</v>
       </c>
     </row>
     <row r="102">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>26.97107765829147</v>
+        <v>33.78588499163227</v>
       </c>
     </row>
     <row r="103">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>35.15338565707082</v>
+        <v>28.03025658519991</v>
       </c>
     </row>
     <row r="104">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>31.16660812426296</v>
+        <v>28.43666063509095</v>
       </c>
     </row>
     <row r="105">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>26.07402228082923</v>
+        <v>26.8584301609489</v>
       </c>
     </row>
     <row r="106">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>25.8647986739715</v>
+        <v>27.26158872920429</v>
       </c>
     </row>
     <row r="107">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>28.2838460125965</v>
+        <v>27.95085293618529</v>
       </c>
     </row>
     <row r="108">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>27.48062625858671</v>
+        <v>34.39454954649837</v>
       </c>
     </row>
     <row r="109">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>35.01878989347505</v>
+        <v>28.03044519907945</v>
       </c>
     </row>
     <row r="110">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>31.3934679667017</v>
+        <v>28.33320417883096</v>
       </c>
     </row>
     <row r="111">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>26.09381547359628</v>
+        <v>27.29887272527676</v>
       </c>
     </row>
     <row r="112">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>26.51764128082209</v>
+        <v>26.56383888647155</v>
       </c>
     </row>
     <row r="113">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>27.88225441176042</v>
+        <v>27.65405982589132</v>
       </c>
     </row>
     <row r="114">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>27.29041638394833</v>
+        <v>33.98652230222712</v>
       </c>
     </row>
     <row r="115">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>34.94483078341526</v>
+        <v>27.4837029083912</v>
       </c>
     </row>
     <row r="116">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>31.4013184370991</v>
+        <v>28.75317939555104</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>26.24566214728613</v>
+        <v>27.03394230760739</v>
       </c>
     </row>
     <row r="118">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>25.89779559253629</v>
+        <v>26.56668746534002</v>
       </c>
     </row>
     <row r="119">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>28.06443578882385</v>
+        <v>27.99304451912765</v>
       </c>
     </row>
     <row r="120">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>26.60670688796073</v>
+        <v>33.98543774302282</v>
       </c>
     </row>
     <row r="121">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>34.84636486328537</v>
+        <v>27.56500925177433</v>
       </c>
     </row>
     <row r="122">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>31.76615727823775</v>
+        <v>28.5325949951568</v>
       </c>
     </row>
     <row r="123">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>25.9390720034709</v>
+        <v>27.0868549502062</v>
       </c>
     </row>
     <row r="124">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>25.85954400904694</v>
+        <v>26.80191462014005</v>
       </c>
     </row>
     <row r="125">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>28.21383865830366</v>
+        <v>27.70449182207439</v>
       </c>
     </row>
     <row r="126">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>26.72814032106296</v>
+        <v>34.36790663820699</v>
       </c>
     </row>
     <row r="127">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>34.64453195394243</v>
+        <v>27.59423479173436</v>
       </c>
     </row>
     <row r="128">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>31.47097013898085</v>
+        <v>28.33191784546669</v>
       </c>
     </row>
     <row r="129">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>25.66552949655757</v>
+        <v>26.56609075685861</v>
       </c>
     </row>
     <row r="130">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>26.50243185409136</v>
+        <v>26.96032109911151</v>
       </c>
     </row>
     <row r="131">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>28.33137234773483</v>
+        <v>27.80894017750828</v>
       </c>
     </row>
     <row r="132">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>27.15504774967263</v>
+        <v>34.15108141537428</v>
       </c>
     </row>
     <row r="133">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>34.94124497445276</v>
+        <v>27.94496406936286</v>
       </c>
     </row>
     <row r="134">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>31.59135967105821</v>
+        <v>28.38256087534469</v>
       </c>
     </row>
     <row r="135">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>26.17377863443622</v>
+        <v>26.59133313222429</v>
       </c>
     </row>
     <row r="136">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>26.29862191614629</v>
+        <v>26.71646367872084</v>
       </c>
     </row>
     <row r="137">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>28.51166242954943</v>
+        <v>27.89112528962128</v>
       </c>
     </row>
     <row r="138">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>27.07428054825322</v>
+        <v>33.9896408594607</v>
       </c>
     </row>
     <row r="139">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>35.22876481341842</v>
+        <v>28.06331256498644</v>
       </c>
     </row>
     <row r="140">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>31.24315742093917</v>
+        <v>27.80968832083029</v>
       </c>
     </row>
     <row r="141">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>25.97096852631566</v>
+        <v>27.26388576513872</v>
       </c>
     </row>
     <row r="142">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>26.13881515716177</v>
+        <v>26.90905462908362</v>
       </c>
     </row>
     <row r="143">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>28.22190756365458</v>
+        <v>27.93250243149319</v>
       </c>
     </row>
     <row r="144">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>26.94485574245162</v>
+        <v>32.94236861163777</v>
       </c>
     </row>
     <row r="145">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>35.20265639865711</v>
+        <v>28.01080847677717</v>
       </c>
     </row>
     <row r="146">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>25.2454369224529</v>
+        <v>30.01595845753423</v>
       </c>
     </row>
     <row r="147">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>24.65065168459432</v>
+        <v>31.10372304704731</v>
       </c>
     </row>
     <row r="148">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>30.73437160711245</v>
+        <v>24.44203430326701</v>
       </c>
     </row>
     <row r="149">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>30.38386961738003</v>
+        <v>24.56642508271634</v>
       </c>
     </row>
     <row r="150">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>26.83645057994356</v>
+        <v>33.83589250670443</v>
       </c>
     </row>
     <row r="151">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>28.53884566671762</v>
+        <v>26.7666514775902</v>
       </c>
     </row>
     <row r="152">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>24.69303058353863</v>
+        <v>30.57467358710738</v>
       </c>
     </row>
     <row r="153">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>24.39990291450822</v>
+        <v>31.34151116223118</v>
       </c>
     </row>
     <row r="154">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>31.22313150322787</v>
+        <v>24.58563555311456</v>
       </c>
     </row>
     <row r="155">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>29.5518064426651</v>
+        <v>24.19987124845317</v>
       </c>
     </row>
     <row r="156">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>27.08586387609199</v>
+        <v>33.36840891978602</v>
       </c>
     </row>
     <row r="157">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>28.7502477512013</v>
+        <v>26.76734647018077</v>
       </c>
     </row>
     <row r="158">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>24.8753287559818</v>
+        <v>30.58115026703895</v>
       </c>
     </row>
     <row r="159">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>24.69671823861944</v>
+        <v>31.48871730480665</v>
       </c>
     </row>
     <row r="160">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>31.06644062796334</v>
+        <v>24.35785309259748</v>
       </c>
     </row>
     <row r="161">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>30.25199661017281</v>
+        <v>24.68951092999813</v>
       </c>
     </row>
     <row r="162">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>26.3248197996779</v>
+        <v>33.230490010339</v>
       </c>
     </row>
     <row r="163">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>29.05459637135672</v>
+        <v>26.81560403534245</v>
       </c>
     </row>
     <row r="164">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>25.29149999606962</v>
+        <v>30.24813273846242</v>
       </c>
     </row>
     <row r="165">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>24.29595918587343</v>
+        <v>31.78895270879044</v>
       </c>
     </row>
     <row r="166">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>30.51166139778628</v>
+        <v>24.11129500588596</v>
       </c>
     </row>
     <row r="167">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>30.08354579095861</v>
+        <v>24.89819069735942</v>
       </c>
     </row>
     <row r="168">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>26.53337038774632</v>
+        <v>33.4993833735863</v>
       </c>
     </row>
     <row r="169">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>28.49462511066238</v>
+        <v>26.4291077951638</v>
       </c>
     </row>
     <row r="170">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>25.02140645402343</v>
+        <v>30.38633692365726</v>
       </c>
     </row>
     <row r="171">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>24.13593327795689</v>
+        <v>31.04451607040781</v>
       </c>
     </row>
     <row r="172">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>31.47439005284762</v>
+        <v>24.46609298394882</v>
       </c>
     </row>
     <row r="173">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>30.23879491796025</v>
+        <v>24.28627003480208</v>
       </c>
     </row>
     <row r="174">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>27.18481773638019</v>
+        <v>33.38520702827577</v>
       </c>
     </row>
     <row r="175">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>28.37093995010986</v>
+        <v>26.6589526028059</v>
       </c>
     </row>
     <row r="176">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>24.56611670888278</v>
+        <v>30.05382767177125</v>
       </c>
     </row>
     <row r="177">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>24.60357067110687</v>
+        <v>31.02228368551049</v>
       </c>
     </row>
     <row r="178">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>31.04132923962453</v>
+        <v>24.14769038360238</v>
       </c>
     </row>
     <row r="179">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>29.58025113051571</v>
+        <v>24.34344773343273</v>
       </c>
     </row>
     <row r="180">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>27.2861030127098</v>
+        <v>34.06188352464204</v>
       </c>
     </row>
     <row r="181">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>28.96399605211875</v>
+        <v>26.30535846012112</v>
       </c>
     </row>
     <row r="182">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>24.90857045489066</v>
+        <v>30.10536344007395</v>
       </c>
     </row>
     <row r="183">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>24.8913856121838</v>
+        <v>31.32306467896732</v>
       </c>
     </row>
     <row r="184">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>31.15390579616358</v>
+        <v>24.3930168091198</v>
       </c>
     </row>
     <row r="185">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>29.88301959108571</v>
+        <v>25.01189998098078</v>
       </c>
     </row>
     <row r="186">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>26.75237285708835</v>
+        <v>33.56626759158525</v>
       </c>
     </row>
     <row r="187">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>28.83284168933913</v>
+        <v>26.61871551683793</v>
       </c>
     </row>
     <row r="188">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>24.72444613797805</v>
+        <v>30.61346676928287</v>
       </c>
     </row>
     <row r="189">
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>24.54445970954584</v>
+        <v>31.55148554698241</v>
       </c>
     </row>
     <row r="190">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>30.95144119721249</v>
+        <v>24.54091954258821</v>
       </c>
     </row>
     <row r="191">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>29.85906661290428</v>
+        <v>24.42732051027088</v>
       </c>
     </row>
     <row r="192">
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>27.19947045757154</v>
+        <v>34.30140780619908</v>
       </c>
     </row>
     <row r="193">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>28.26061668298004</v>
+        <v>26.50331663324251</v>
       </c>
     </row>
     <row r="194">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>33.12214443720367</v>
+        <v>29.27424342118513</v>
       </c>
     </row>
     <row r="195">
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>28.23148885419108</v>
+        <v>26.05729149668716</v>
       </c>
     </row>
     <row r="196">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>36.712635360508</v>
+        <v>23.18683769101989</v>
       </c>
     </row>
     <row r="197">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>23.32201849253753</v>
+        <v>30.62035401070132</v>
       </c>
     </row>
     <row r="198">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>31.87141059007394</v>
+        <v>32.18018570043371</v>
       </c>
     </row>
     <row r="199">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>30.39347236940185</v>
+        <v>29.05524840160739</v>
       </c>
     </row>
     <row r="200">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>33.28334352298464</v>
+        <v>29.34388103923992</v>
       </c>
     </row>
     <row r="201">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>28.00485191096907</v>
+        <v>26.8141446381162</v>
       </c>
     </row>
     <row r="202">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>35.77843992022503</v>
+        <v>23.1620995707544</v>
       </c>
     </row>
     <row r="203">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>23.34017381386759</v>
+        <v>30.09715006828912</v>
       </c>
     </row>
     <row r="204">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>32.10890429508083</v>
+        <v>32.90911821179393</v>
       </c>
     </row>
     <row r="205">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>30.02532087597112</v>
+        <v>28.99951535806682</v>
       </c>
     </row>
     <row r="206">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>32.94783538120974</v>
+        <v>29.24252976019879</v>
       </c>
     </row>
     <row r="207">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>27.77453459140841</v>
+        <v>26.20543578293931</v>
       </c>
     </row>
     <row r="208">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>36.10908188621413</v>
+        <v>23.2970796428705</v>
       </c>
     </row>
     <row r="209">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>23.61042245651111</v>
+        <v>30.479304963994</v>
       </c>
     </row>
     <row r="210">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>32.15787921856627</v>
+        <v>32.18894587171851</v>
       </c>
     </row>
     <row r="211">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>30.29260923476754</v>
+        <v>29.04942350353667</v>
       </c>
     </row>
     <row r="212">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>33.33014096144546</v>
+        <v>29.22758890908549</v>
       </c>
     </row>
     <row r="213">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>27.81697721649121</v>
+        <v>26.49321476792213</v>
       </c>
     </row>
     <row r="214">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>36.25276202941521</v>
+        <v>24.00841693244885</v>
       </c>
     </row>
     <row r="215">
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>23.30715971375989</v>
+        <v>30.27027928184404</v>
       </c>
     </row>
     <row r="216">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>32.46940933326956</v>
+        <v>33.41226676364774</v>
       </c>
     </row>
     <row r="217">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>30.54204111785763</v>
+        <v>28.96505765519993</v>
       </c>
     </row>
     <row r="218">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>33.80183156274949</v>
+        <v>29.120037515158</v>
       </c>
     </row>
     <row r="219">
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>28.16874035705878</v>
+        <v>26.68456871243691</v>
       </c>
     </row>
     <row r="220">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>35.87977313515012</v>
+        <v>23.71713757116262</v>
       </c>
     </row>
     <row r="221">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>23.68470853867535</v>
+        <v>30.37217056438397</v>
       </c>
     </row>
     <row r="222">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>32.18637500943603</v>
+        <v>33.18041963549859</v>
       </c>
     </row>
     <row r="223">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>30.29433448070104</v>
+        <v>29.13658970189278</v>
       </c>
     </row>
     <row r="224">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>33.80647172092494</v>
+        <v>29.38376514616875</v>
       </c>
     </row>
     <row r="225">
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>28.49528052530744</v>
+        <v>25.87879645229173</v>
       </c>
     </row>
     <row r="226">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>36.12347549607</v>
+        <v>23.53043304836974</v>
       </c>
     </row>
     <row r="227">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>23.05591793370286</v>
+        <v>30.5601103472412</v>
       </c>
     </row>
     <row r="228">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>32.02616994069103</v>
+        <v>32.91350933882234</v>
       </c>
     </row>
     <row r="229">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>30.76780719812139</v>
+        <v>29.31909927830198</v>
       </c>
     </row>
     <row r="230">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>33.68174009178319</v>
+        <v>29.51692888076704</v>
       </c>
     </row>
     <row r="231">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>28.07451648002358</v>
+        <v>25.99637025080335</v>
       </c>
     </row>
     <row r="232">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>36.1721674080357</v>
+        <v>23.283015283901</v>
       </c>
     </row>
     <row r="233">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>23.51975560846318</v>
+        <v>30.32308614526009</v>
       </c>
     </row>
     <row r="234">
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>31.98110782119507</v>
+        <v>32.7812133225522</v>
       </c>
     </row>
     <row r="235">
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>30.86440080743927</v>
+        <v>29.15463601225715</v>
       </c>
     </row>
     <row r="236">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>33.16096591887466</v>
+        <v>29.19295645471029</v>
       </c>
     </row>
     <row r="237">
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>28.03558463293858</v>
+        <v>26.06527926695863</v>
       </c>
     </row>
     <row r="238">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>36.09437301268058</v>
+        <v>23.84272825228502</v>
       </c>
     </row>
     <row r="239">
@@ -4243,7 +4243,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>23.15968451165134</v>
+        <v>30.41583300917204</v>
       </c>
     </row>
     <row r="240">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>31.96039921782907</v>
+        <v>32.7223909464002</v>
       </c>
     </row>
     <row r="241">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>30.96030616245157</v>
+        <v>29.06203744712472</v>
       </c>
     </row>
     <row r="242">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>31.35340337812626</v>
+        <v>31.73118220277987</v>
       </c>
     </row>
     <row r="243">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>27.22477451427451</v>
+        <v>29.68022382953615</v>
       </c>
     </row>
     <row r="244">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>25.39471159120684</v>
+        <v>26.67014733161639</v>
       </c>
     </row>
     <row r="245">
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>29.52956437281675</v>
+        <v>27.30200516002901</v>
       </c>
     </row>
     <row r="246">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>31.67335933432178</v>
+        <v>33.97616635853068</v>
       </c>
     </row>
     <row r="247">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>28.18939754768148</v>
+        <v>25.11140858821591</v>
       </c>
     </row>
     <row r="248">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>31.01258234303373</v>
+        <v>31.05186253934166</v>
       </c>
     </row>
     <row r="249">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>27.16705038568502</v>
+        <v>29.24352147922601</v>
       </c>
     </row>
     <row r="250">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>24.08681504612368</v>
+        <v>26.55948005471292</v>
       </c>
     </row>
     <row r="251">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>29.2035457860262</v>
+        <v>27.74977901547832</v>
       </c>
     </row>
     <row r="252">
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>32.07673458933353</v>
+        <v>33.60023631521796</v>
       </c>
     </row>
     <row r="253">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>28.36662932997892</v>
+        <v>24.28400554535049</v>
       </c>
     </row>
     <row r="254">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>31.07160443379853</v>
+        <v>31.26560225980927</v>
       </c>
     </row>
     <row r="255">
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>27.45054486594428</v>
+        <v>29.7702778414431</v>
       </c>
     </row>
     <row r="256">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>24.76409983489562</v>
+        <v>26.4050225487516</v>
       </c>
     </row>
     <row r="257">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>29.68283169368442</v>
+        <v>27.67598628345977</v>
       </c>
     </row>
     <row r="258">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>32.90521013924698</v>
+        <v>34.02267510264643</v>
       </c>
     </row>
     <row r="259">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>28.57228910298437</v>
+        <v>24.60144717904295</v>
       </c>
     </row>
     <row r="260">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>31.48173668741785</v>
+        <v>31.29084111834331</v>
       </c>
     </row>
     <row r="261">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>27.9723502081715</v>
+        <v>29.83871279671071</v>
       </c>
     </row>
     <row r="262">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>24.48108061675891</v>
+        <v>26.2859611601673</v>
       </c>
     </row>
     <row r="263">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>28.83315531671206</v>
+        <v>27.24630635832627</v>
       </c>
     </row>
     <row r="264">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>32.42007813680029</v>
+        <v>33.54132070052047</v>
       </c>
     </row>
     <row r="265">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>28.98865823513544</v>
+        <v>24.4217691459387</v>
       </c>
     </row>
     <row r="266">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>31.5209887786927</v>
+        <v>31.04814592202665</v>
       </c>
     </row>
     <row r="267">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>27.37754381930883</v>
+        <v>30.13497841494731</v>
       </c>
     </row>
     <row r="268">
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>24.50871436021695</v>
+        <v>27.08879787436165</v>
       </c>
     </row>
     <row r="269">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>29.52023040452965</v>
+        <v>27.41163638707199</v>
       </c>
     </row>
     <row r="270">
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>32.7565430704362</v>
+        <v>33.66181752372033</v>
       </c>
     </row>
     <row r="271">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>28.57334643094002</v>
+        <v>24.49638730237768</v>
       </c>
     </row>
     <row r="272">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>31.38615861125379</v>
+        <v>31.64623136231488</v>
       </c>
     </row>
     <row r="273">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>27.23396981835268</v>
+        <v>29.97966608655916</v>
       </c>
     </row>
     <row r="274">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>24.54571391242157</v>
+        <v>26.04173378675746</v>
       </c>
     </row>
     <row r="275">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>29.26813382340342</v>
+        <v>27.63988239445186</v>
       </c>
     </row>
     <row r="276">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>32.09670084738454</v>
+        <v>33.19147483637172</v>
       </c>
     </row>
     <row r="277">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>28.01585298559013</v>
+        <v>24.97401234908027</v>
       </c>
     </row>
     <row r="278">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>31.45107503678725</v>
+        <v>31.43738447831295</v>
       </c>
     </row>
     <row r="279">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>27.29363916857805</v>
+        <v>29.3496265477949</v>
       </c>
     </row>
     <row r="280">
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>24.73349760262966</v>
+        <v>26.44895725577802</v>
       </c>
     </row>
     <row r="281">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>29.38001170138705</v>
+        <v>27.42944231231599</v>
       </c>
     </row>
     <row r="282">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>32.47291230857922</v>
+        <v>33.80757213425103</v>
       </c>
     </row>
     <row r="283">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>28.26795518576671</v>
+        <v>24.79819988724254</v>
       </c>
     </row>
     <row r="284">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>31.64270176013494</v>
+        <v>30.94020449648892</v>
       </c>
     </row>
     <row r="285">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>27.15584987229415</v>
+        <v>30.13743052202079</v>
       </c>
     </row>
     <row r="286">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>24.89345814847049</v>
+        <v>26.93865428045719</v>
       </c>
     </row>
     <row r="287">
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>29.28764807939944</v>
+        <v>27.26814467616272</v>
       </c>
     </row>
     <row r="288">
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>31.95956588557389</v>
+        <v>33.6554555005744</v>
       </c>
     </row>
     <row r="289">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>28.63192206010705</v>
+        <v>24.96236359708143</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios168.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios168.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.52165756798313</v>
+        <v>29.1784079253104</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.38387118486623</v>
+        <v>32.14286756732267</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.4268945511024</v>
+        <v>28.1049817066979</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26.71015322597733</v>
+        <v>21.75021413556262</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.90327033877592</v>
+        <v>33.31199147811808</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.22450875083157</v>
+        <v>29.8003454302729</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.08480830583128</v>
+        <v>28.67925480203631</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29.65143004118822</v>
+        <v>31.86056446155584</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29.66144519149528</v>
+        <v>28.10955636492739</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>26.28856753705578</v>
+        <v>21.5603071520227</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32.01999030736107</v>
+        <v>33.98664685414833</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.13186484374422</v>
+        <v>29.99554872427842</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.53659596134007</v>
+        <v>28.65162529482005</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>29.56151625091952</v>
+        <v>31.86548615367547</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29.82270251973921</v>
+        <v>28.01963497005248</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26.74411212859321</v>
+        <v>21.15920618135383</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.16622267263315</v>
+        <v>33.45981575591713</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17.13117351291829</v>
+        <v>29.45863956187271</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25.66329438406707</v>
+        <v>28.94538365433128</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29.42187477489548</v>
+        <v>31.47327383862805</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29.47798607026893</v>
+        <v>27.90301847548536</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.59429358720882</v>
+        <v>21.25684846928692</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32.05499077583924</v>
+        <v>33.93078719607878</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.33188781212301</v>
+        <v>29.23038624351602</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>25.573210997774</v>
+        <v>28.80146267703318</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29.28698439238419</v>
+        <v>32.14197885088493</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29.4443278254637</v>
+        <v>28.40242124357959</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26.87318216998078</v>
+        <v>21.53977858220783</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31.87028213967497</v>
+        <v>33.57336755293929</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.96422312812221</v>
+        <v>29.39567706995171</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>25.76957151031728</v>
+        <v>28.20403442261238</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>29.4403418554765</v>
+        <v>32.26273480062805</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.90498663723931</v>
+        <v>28.25834661820356</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>27.10947223037629</v>
+        <v>21.07498411472184</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31.92593680308753</v>
+        <v>33.11902014070917</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16.93609215199885</v>
+        <v>29.63422238920945</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>25.35736709499716</v>
+        <v>28.83378654394128</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>29.29956250865406</v>
+        <v>31.86439254291801</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>29.65804627634915</v>
+        <v>27.94786484969616</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>26.71831981791384</v>
+        <v>21.01896526008282</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>32.2778007836954</v>
+        <v>33.99454517036055</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17.32688254997114</v>
+        <v>29.17539644646502</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25.63544745846339</v>
+        <v>28.89215511728181</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>29.76695898963087</v>
+        <v>32.17196321767971</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>29.03980672382814</v>
+        <v>28.47172485736952</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>26.89208652087522</v>
+        <v>21.24255887022943</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32.71586025416065</v>
+        <v>33.55325093693501</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16.57372725114038</v>
+        <v>29.05758578333833</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>25.34379021237217</v>
+        <v>31.14321044516182</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>31.5683578239161</v>
+        <v>22.78432568717093</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>24.91415597807234</v>
+        <v>22.99638714714938</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>22.96834626433409</v>
+        <v>26.29148743383685</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>28.38046755988312</v>
+        <v>27.7545058654045</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>22.57238005821834</v>
+        <v>33.03836195679813</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>25.07684074056399</v>
+        <v>31.54779975273271</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>31.32043168733076</v>
+        <v>22.28947632602096</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>25.16403141385614</v>
+        <v>23.53363400590807</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.98476131801954</v>
+        <v>26.70533295967546</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>27.79540049890607</v>
+        <v>27.29467515167047</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22.33369603119942</v>
+        <v>32.53006348923995</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>25.88057586345958</v>
+        <v>31.5921616542722</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>31.95980121360029</v>
+        <v>22.77872568625374</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>25.41669059758798</v>
+        <v>23.70198842993917</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>22.45306482073803</v>
+        <v>26.02496990945845</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>27.70607176242047</v>
+        <v>27.06495845985492</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22.41546590202501</v>
+        <v>33.56086451848</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>24.91828172573777</v>
+        <v>31.7025488536846</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>32.12477054632016</v>
+        <v>22.70653888825625</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>25.4820687326714</v>
+        <v>23.25232811733004</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>22.66423009812685</v>
+        <v>26.48073950365241</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28.40117542917169</v>
+        <v>27.74042832825317</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.3977857411417</v>
+        <v>32.89181152553862</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>25.82202716262642</v>
+        <v>32.31174131654173</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>31.6644929439812</v>
+        <v>22.57525530659693</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>25.27247375775722</v>
+        <v>23.35278695723776</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>23.10478192184185</v>
+        <v>26.41260580334836</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>28.2599046214408</v>
+        <v>27.60439171571671</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>22.51313569533058</v>
+        <v>32.86824975492559</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>25.13474535917969</v>
+        <v>31.3509489289509</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>31.78130731271219</v>
+        <v>22.72004291429216</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>24.92260160347242</v>
+        <v>23.32672887888342</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>22.82046757494239</v>
+        <v>26.19852957343853</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>27.59386692446979</v>
+        <v>27.48556087323534</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21.9998431417018</v>
+        <v>32.47818095235531</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>25.18296331280413</v>
+        <v>31.39827716497157</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>32.01786143282236</v>
+        <v>22.05687616097726</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>25.36032314940595</v>
+        <v>23.82344322491384</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>22.76713831186366</v>
+        <v>26.49807070740587</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>28.39087100759761</v>
+        <v>27.44455304484879</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>22.27127558626301</v>
+        <v>32.57469203638053</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>24.68754708604166</v>
+        <v>30.84546936062914</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>30.92879196134141</v>
+        <v>22.48425413678821</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>24.83088383476776</v>
+        <v>23.58195452309466</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>22.97187718862755</v>
+        <v>26.59990471918312</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>27.72626991743568</v>
+        <v>27.65311612979883</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>22.50198707635457</v>
+        <v>32.84544013702924</v>
       </c>
     </row>
     <row r="98">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>28.98820977878366</v>
+        <v>29.3435518030263</v>
       </c>
     </row>
     <row r="99">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>26.66529023268927</v>
+        <v>27.80597526410832</v>
       </c>
     </row>
     <row r="100">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>26.82558280571372</v>
+        <v>28.45834382712525</v>
       </c>
     </row>
     <row r="101">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>27.95535640600297</v>
+        <v>29.48023116990239</v>
       </c>
     </row>
     <row r="102">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>33.78588499163227</v>
+        <v>19.81913482729941</v>
       </c>
     </row>
     <row r="103">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>28.03025658519991</v>
+        <v>23.24307218664672</v>
       </c>
     </row>
     <row r="104">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>28.43666063509095</v>
+        <v>28.6575325859875</v>
       </c>
     </row>
     <row r="105">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>26.8584301609489</v>
+        <v>28.08149371654811</v>
       </c>
     </row>
     <row r="106">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>27.26158872920429</v>
+        <v>27.94372849436616</v>
       </c>
     </row>
     <row r="107">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>27.95085293618529</v>
+        <v>29.28832965223571</v>
       </c>
     </row>
     <row r="108">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>34.39454954649837</v>
+        <v>20.13803552257995</v>
       </c>
     </row>
     <row r="109">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>28.03044519907945</v>
+        <v>23.55621044742037</v>
       </c>
     </row>
     <row r="110">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>28.33320417883096</v>
+        <v>29.24469644417276</v>
       </c>
     </row>
     <row r="111">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>27.29887272527676</v>
+        <v>28.04063247239765</v>
       </c>
     </row>
     <row r="112">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>26.56383888647155</v>
+        <v>27.94081016919655</v>
       </c>
     </row>
     <row r="113">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>27.65405982589132</v>
+        <v>29.616566453215</v>
       </c>
     </row>
     <row r="114">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>33.98652230222712</v>
+        <v>20.02034261239012</v>
       </c>
     </row>
     <row r="115">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>27.4837029083912</v>
+        <v>23.26339445385713</v>
       </c>
     </row>
     <row r="116">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>28.75317939555104</v>
+        <v>28.64590900020319</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>27.03394230760739</v>
+        <v>27.70772416914889</v>
       </c>
     </row>
     <row r="118">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>26.56668746534002</v>
+        <v>28.72618802800177</v>
       </c>
     </row>
     <row r="119">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>27.99304451912765</v>
+        <v>29.47189699847318</v>
       </c>
     </row>
     <row r="120">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>33.98543774302282</v>
+        <v>20.24183755126548</v>
       </c>
     </row>
     <row r="121">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>27.56500925177433</v>
+        <v>23.36916784050673</v>
       </c>
     </row>
     <row r="122">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>28.5325949951568</v>
+        <v>29.22333319635675</v>
       </c>
     </row>
     <row r="123">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>27.0868549502062</v>
+        <v>28.14940313771654</v>
       </c>
     </row>
     <row r="124">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>26.80191462014005</v>
+        <v>28.42101361949105</v>
       </c>
     </row>
     <row r="125">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>27.70449182207439</v>
+        <v>29.70881846692722</v>
       </c>
     </row>
     <row r="126">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>34.36790663820699</v>
+        <v>20.27073074885375</v>
       </c>
     </row>
     <row r="127">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>27.59423479173436</v>
+        <v>23.56804011149693</v>
       </c>
     </row>
     <row r="128">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>28.33191784546669</v>
+        <v>29.46221212016128</v>
       </c>
     </row>
     <row r="129">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>26.56609075685861</v>
+        <v>27.44571013800523</v>
       </c>
     </row>
     <row r="130">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>26.96032109911151</v>
+        <v>28.25088485384506</v>
       </c>
     </row>
     <row r="131">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>27.80894017750828</v>
+        <v>29.67789158062618</v>
       </c>
     </row>
     <row r="132">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>34.15108141537428</v>
+        <v>19.80806171059486</v>
       </c>
     </row>
     <row r="133">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>27.94496406936286</v>
+        <v>23.61528737620021</v>
       </c>
     </row>
     <row r="134">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>28.38256087534469</v>
+        <v>28.53425781088107</v>
       </c>
     </row>
     <row r="135">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>26.59133313222429</v>
+        <v>27.71512744210231</v>
       </c>
     </row>
     <row r="136">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>26.71646367872084</v>
+        <v>27.59003256853306</v>
       </c>
     </row>
     <row r="137">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>27.89112528962128</v>
+        <v>30.05530529776012</v>
       </c>
     </row>
     <row r="138">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>33.9896408594607</v>
+        <v>19.94902280152414</v>
       </c>
     </row>
     <row r="139">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>28.06331256498644</v>
+        <v>23.98797276287647</v>
       </c>
     </row>
     <row r="140">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>27.80968832083029</v>
+        <v>29.19845472845116</v>
       </c>
     </row>
     <row r="141">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>27.26388576513872</v>
+        <v>28.02263813937064</v>
       </c>
     </row>
     <row r="142">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>26.90905462908362</v>
+        <v>27.98779270991825</v>
       </c>
     </row>
     <row r="143">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>27.93250243149319</v>
+        <v>29.28438737312343</v>
       </c>
     </row>
     <row r="144">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>32.94236861163777</v>
+        <v>20.09989171760199</v>
       </c>
     </row>
     <row r="145">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>28.01080847677717</v>
+        <v>23.46241468384382</v>
       </c>
     </row>
     <row r="146">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>30.01595845753423</v>
+        <v>24.56939580123904</v>
       </c>
     </row>
     <row r="147">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>31.10372304704731</v>
+        <v>28.67913488954688</v>
       </c>
     </row>
     <row r="148">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>24.44203430326701</v>
+        <v>24.63485814168267</v>
       </c>
     </row>
     <row r="149">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>24.56642508271634</v>
+        <v>28.55374057069583</v>
       </c>
     </row>
     <row r="150">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>33.83589250670443</v>
+        <v>24.29041387286073</v>
       </c>
     </row>
     <row r="151">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>26.7666514775902</v>
+        <v>24.84239636461746</v>
       </c>
     </row>
     <row r="152">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>30.57467358710738</v>
+        <v>24.94000421955833</v>
       </c>
     </row>
     <row r="153">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>31.34151116223118</v>
+        <v>29.02291768608655</v>
       </c>
     </row>
     <row r="154">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>24.58563555311456</v>
+        <v>24.64088205694563</v>
       </c>
     </row>
     <row r="155">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>24.19987124845317</v>
+        <v>28.42872781511417</v>
       </c>
     </row>
     <row r="156">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>33.36840891978602</v>
+        <v>24.20968570542447</v>
       </c>
     </row>
     <row r="157">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>26.76734647018077</v>
+        <v>24.57008364915065</v>
       </c>
     </row>
     <row r="158">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>30.58115026703895</v>
+        <v>24.88228395499255</v>
       </c>
     </row>
     <row r="159">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>31.48871730480665</v>
+        <v>28.98985213843883</v>
       </c>
     </row>
     <row r="160">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>24.35785309259748</v>
+        <v>24.76879217598879</v>
       </c>
     </row>
     <row r="161">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>24.68951092999813</v>
+        <v>28.37565044283756</v>
       </c>
     </row>
     <row r="162">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>33.230490010339</v>
+        <v>23.45266042917345</v>
       </c>
     </row>
     <row r="163">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>26.81560403534245</v>
+        <v>24.90722151316249</v>
       </c>
     </row>
     <row r="164">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>30.24813273846242</v>
+        <v>25.08426562760649</v>
       </c>
     </row>
     <row r="165">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>31.78895270879044</v>
+        <v>29.07946142075861</v>
       </c>
     </row>
     <row r="166">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>24.11129500588596</v>
+        <v>25.09545519880638</v>
       </c>
     </row>
     <row r="167">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>24.89819069735942</v>
+        <v>28.08449131201619</v>
       </c>
     </row>
     <row r="168">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>33.4993833735863</v>
+        <v>24.05368487233261</v>
       </c>
     </row>
     <row r="169">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>26.4291077951638</v>
+        <v>24.41419763373285</v>
       </c>
     </row>
     <row r="170">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>30.38633692365726</v>
+        <v>24.81605792415733</v>
       </c>
     </row>
     <row r="171">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>31.04451607040781</v>
+        <v>29.09994445815295</v>
       </c>
     </row>
     <row r="172">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>24.46609298394882</v>
+        <v>24.20865290140781</v>
       </c>
     </row>
     <row r="173">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>24.28627003480208</v>
+        <v>27.73855053050503</v>
       </c>
     </row>
     <row r="174">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>33.38520702827577</v>
+        <v>23.57109344055682</v>
       </c>
     </row>
     <row r="175">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>26.6589526028059</v>
+        <v>25.02665153661965</v>
       </c>
     </row>
     <row r="176">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>30.05382767177125</v>
+        <v>24.72688853994693</v>
       </c>
     </row>
     <row r="177">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>31.02228368551049</v>
+        <v>28.8826254482954</v>
       </c>
     </row>
     <row r="178">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>24.14769038360238</v>
+        <v>25.07665543487438</v>
       </c>
     </row>
     <row r="179">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>24.34344773343273</v>
+        <v>27.58937312005859</v>
       </c>
     </row>
     <row r="180">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>34.06188352464204</v>
+        <v>23.27222118406398</v>
       </c>
     </row>
     <row r="181">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>26.30535846012112</v>
+        <v>24.70193189265472</v>
       </c>
     </row>
     <row r="182">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>30.10536344007395</v>
+        <v>24.54239196565461</v>
       </c>
     </row>
     <row r="183">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>31.32306467896732</v>
+        <v>28.71034636841949</v>
       </c>
     </row>
     <row r="184">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>24.3930168091198</v>
+        <v>25.01595160370697</v>
       </c>
     </row>
     <row r="185">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>25.01189998098078</v>
+        <v>28.28873527012918</v>
       </c>
     </row>
     <row r="186">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>33.56626759158525</v>
+        <v>23.95190992252882</v>
       </c>
     </row>
     <row r="187">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>26.61871551683793</v>
+        <v>25.06645953570658</v>
       </c>
     </row>
     <row r="188">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>30.61346676928287</v>
+        <v>25.21199172587576</v>
       </c>
     </row>
     <row r="189">
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>31.55148554698241</v>
+        <v>28.50099334871011</v>
       </c>
     </row>
     <row r="190">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>24.54091954258821</v>
+        <v>24.98535199033547</v>
       </c>
     </row>
     <row r="191">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>24.42732051027088</v>
+        <v>27.8945667020748</v>
       </c>
     </row>
     <row r="192">
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>34.30140780619908</v>
+        <v>23.58681956121402</v>
       </c>
     </row>
     <row r="193">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>26.50331663324251</v>
+        <v>24.9305119449803</v>
       </c>
     </row>
     <row r="194">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>29.27424342118513</v>
+        <v>31.6761364009524</v>
       </c>
     </row>
     <row r="195">
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>26.05729149668716</v>
+        <v>31.38704136769855</v>
       </c>
     </row>
     <row r="196">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>23.18683769101989</v>
+        <v>28.98605888817417</v>
       </c>
     </row>
     <row r="197">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>30.62035401070132</v>
+        <v>24.37903746693189</v>
       </c>
     </row>
     <row r="198">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>32.18018570043371</v>
+        <v>33.8243912463378</v>
       </c>
     </row>
     <row r="199">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>29.05524840160739</v>
+        <v>28.5699859969923</v>
       </c>
     </row>
     <row r="200">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>29.34388103923992</v>
+        <v>32.47364286524822</v>
       </c>
     </row>
     <row r="201">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>26.8141446381162</v>
+        <v>32.16379123413089</v>
       </c>
     </row>
     <row r="202">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>23.1620995707544</v>
+        <v>28.82813807964124</v>
       </c>
     </row>
     <row r="203">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>30.09715006828912</v>
+        <v>23.97507088570587</v>
       </c>
     </row>
     <row r="204">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>32.90911821179393</v>
+        <v>33.63456414925758</v>
       </c>
     </row>
     <row r="205">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>28.99951535806682</v>
+        <v>29.06510269605828</v>
       </c>
     </row>
     <row r="206">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>29.24252976019879</v>
+        <v>32.66168292632057</v>
       </c>
     </row>
     <row r="207">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>26.20543578293931</v>
+        <v>31.8421416720291</v>
       </c>
     </row>
     <row r="208">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>23.2970796428705</v>
+        <v>28.73165261480576</v>
       </c>
     </row>
     <row r="209">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>30.479304963994</v>
+        <v>24.22147027347694</v>
       </c>
     </row>
     <row r="210">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>32.18894587171851</v>
+        <v>33.87105933418123</v>
       </c>
     </row>
     <row r="211">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>29.04942350353667</v>
+        <v>28.65612422909799</v>
       </c>
     </row>
     <row r="212">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>29.22758890908549</v>
+        <v>31.30096965756849</v>
       </c>
     </row>
     <row r="213">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>26.49321476792213</v>
+        <v>32.32750600742654</v>
       </c>
     </row>
     <row r="214">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>24.00841693244885</v>
+        <v>29.32050177558019</v>
       </c>
     </row>
     <row r="215">
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>30.27027928184404</v>
+        <v>24.11212470288571</v>
       </c>
     </row>
     <row r="216">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>33.41226676364774</v>
+        <v>33.41790904302122</v>
       </c>
     </row>
     <row r="217">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>28.96505765519993</v>
+        <v>28.78409147627109</v>
       </c>
     </row>
     <row r="218">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>29.120037515158</v>
+        <v>32.17343795769444</v>
       </c>
     </row>
     <row r="219">
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>26.68456871243691</v>
+        <v>32.26449148232372</v>
       </c>
     </row>
     <row r="220">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>23.71713757116262</v>
+        <v>28.81930544457508</v>
       </c>
     </row>
     <row r="221">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>30.37217056438397</v>
+        <v>24.06840135370249</v>
       </c>
     </row>
     <row r="222">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>33.18041963549859</v>
+        <v>33.33287035663552</v>
       </c>
     </row>
     <row r="223">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>29.13658970189278</v>
+        <v>29.07311580552394</v>
       </c>
     </row>
     <row r="224">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>29.38376514616875</v>
+        <v>32.42712345077154</v>
       </c>
     </row>
     <row r="225">
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>25.87879645229173</v>
+        <v>32.28526987456708</v>
       </c>
     </row>
     <row r="226">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>23.53043304836974</v>
+        <v>28.52469501352452</v>
       </c>
     </row>
     <row r="227">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>30.5601103472412</v>
+        <v>24.7067147873548</v>
       </c>
     </row>
     <row r="228">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>32.91350933882234</v>
+        <v>33.18921669667754</v>
       </c>
     </row>
     <row r="229">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>29.31909927830198</v>
+        <v>29.0281414169106</v>
       </c>
     </row>
     <row r="230">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>29.51692888076704</v>
+        <v>31.61834515597775</v>
       </c>
     </row>
     <row r="231">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>25.99637025080335</v>
+        <v>31.6939756654029</v>
       </c>
     </row>
     <row r="232">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>23.283015283901</v>
+        <v>29.25319762711396</v>
       </c>
     </row>
     <row r="233">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>30.32308614526009</v>
+        <v>24.46239194257269</v>
       </c>
     </row>
     <row r="234">
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>32.7812133225522</v>
+        <v>33.59370195504734</v>
       </c>
     </row>
     <row r="235">
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>29.15463601225715</v>
+        <v>28.67406123499618</v>
       </c>
     </row>
     <row r="236">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>29.19295645471029</v>
+        <v>32.26631213849152</v>
       </c>
     </row>
     <row r="237">
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>26.06527926695863</v>
+        <v>32.11070839120181</v>
       </c>
     </row>
     <row r="238">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>23.84272825228502</v>
+        <v>29.16406684646584</v>
       </c>
     </row>
     <row r="239">
@@ -4243,7 +4243,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>30.41583300917204</v>
+        <v>24.15001162806256</v>
       </c>
     </row>
     <row r="240">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>32.7223909464002</v>
+        <v>33.23377333948046</v>
       </c>
     </row>
     <row r="241">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>29.06203744712472</v>
+        <v>28.86885281749069</v>
       </c>
     </row>
     <row r="242">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>31.73118220277987</v>
+        <v>28.52905142879737</v>
       </c>
     </row>
     <row r="243">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>29.68022382953615</v>
+        <v>22.0394681355949</v>
       </c>
     </row>
     <row r="244">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>26.67014733161639</v>
+        <v>29.80748459297499</v>
       </c>
     </row>
     <row r="245">
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>27.30200516002901</v>
+        <v>26.2857959910102</v>
       </c>
     </row>
     <row r="246">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>33.97616635853068</v>
+        <v>31.13363424659376</v>
       </c>
     </row>
     <row r="247">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>25.11140858821591</v>
+        <v>26.03179475924729</v>
       </c>
     </row>
     <row r="248">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>31.05186253934166</v>
+        <v>28.79964377803661</v>
       </c>
     </row>
     <row r="249">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>29.24352147922601</v>
+        <v>22.03579163127104</v>
       </c>
     </row>
     <row r="250">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>26.55948005471292</v>
+        <v>29.47302664778764</v>
       </c>
     </row>
     <row r="251">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>27.74977901547832</v>
+        <v>26.27794596894636</v>
       </c>
     </row>
     <row r="252">
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>33.60023631521796</v>
+        <v>31.57913172770454</v>
       </c>
     </row>
     <row r="253">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>24.28400554535049</v>
+        <v>26.47288406454393</v>
       </c>
     </row>
     <row r="254">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>31.26560225980927</v>
+        <v>28.96887680812727</v>
       </c>
     </row>
     <row r="255">
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>29.7702778414431</v>
+        <v>22.64633018002543</v>
       </c>
     </row>
     <row r="256">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>26.4050225487516</v>
+        <v>30.78974672167361</v>
       </c>
     </row>
     <row r="257">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>27.67598628345977</v>
+        <v>26.3528896408888</v>
       </c>
     </row>
     <row r="258">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>34.02267510264643</v>
+        <v>31.47936856765676</v>
       </c>
     </row>
     <row r="259">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>24.60144717904295</v>
+        <v>26.53272228597163</v>
       </c>
     </row>
     <row r="260">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>31.29084111834331</v>
+        <v>28.9456162286502</v>
       </c>
     </row>
     <row r="261">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>29.83871279671071</v>
+        <v>22.72608422202311</v>
       </c>
     </row>
     <row r="262">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>26.2859611601673</v>
+        <v>29.5944045827532</v>
       </c>
     </row>
     <row r="263">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>27.24630635832627</v>
+        <v>26.21057099479673</v>
       </c>
     </row>
     <row r="264">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>33.54132070052047</v>
+        <v>31.13774787395448</v>
       </c>
     </row>
     <row r="265">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>24.4217691459387</v>
+        <v>26.21874678961646</v>
       </c>
     </row>
     <row r="266">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>31.04814592202665</v>
+        <v>28.75143462917027</v>
       </c>
     </row>
     <row r="267">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>30.13497841494731</v>
+        <v>22.67885853406229</v>
       </c>
     </row>
     <row r="268">
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>27.08879787436165</v>
+        <v>29.57691978596269</v>
       </c>
     </row>
     <row r="269">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>27.41163638707199</v>
+        <v>26.26167594396716</v>
       </c>
     </row>
     <row r="270">
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>33.66181752372033</v>
+        <v>31.09260097957196</v>
       </c>
     </row>
     <row r="271">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>24.49638730237768</v>
+        <v>26.20676425815063</v>
       </c>
     </row>
     <row r="272">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>31.64623136231488</v>
+        <v>28.11159482542011</v>
       </c>
     </row>
     <row r="273">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>29.97966608655916</v>
+        <v>22.20035640663547</v>
       </c>
     </row>
     <row r="274">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>26.04173378675746</v>
+        <v>29.92330090103328</v>
       </c>
     </row>
     <row r="275">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>27.63988239445186</v>
+        <v>26.72061189636466</v>
       </c>
     </row>
     <row r="276">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>33.19147483637172</v>
+        <v>30.68012120836992</v>
       </c>
     </row>
     <row r="277">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>24.97401234908027</v>
+        <v>25.96223040852775</v>
       </c>
     </row>
     <row r="278">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>31.43738447831295</v>
+        <v>28.66881685496691</v>
       </c>
     </row>
     <row r="279">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>29.3496265477949</v>
+        <v>21.86642005186358</v>
       </c>
     </row>
     <row r="280">
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>26.44895725577802</v>
+        <v>29.58677952259538</v>
       </c>
     </row>
     <row r="281">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>27.42944231231599</v>
+        <v>25.88462721771499</v>
       </c>
     </row>
     <row r="282">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>33.80757213425103</v>
+        <v>31.46343351998511</v>
       </c>
     </row>
     <row r="283">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>24.79819988724254</v>
+        <v>26.06465787276947</v>
       </c>
     </row>
     <row r="284">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>30.94020449648892</v>
+        <v>29.13385658803995</v>
       </c>
     </row>
     <row r="285">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>30.13743052202079</v>
+        <v>22.57854650536447</v>
       </c>
     </row>
     <row r="286">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>26.93865428045719</v>
+        <v>29.5269411386297</v>
       </c>
     </row>
     <row r="287">
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>27.26814467616272</v>
+        <v>26.0595593730428</v>
       </c>
     </row>
     <row r="288">
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>33.6554555005744</v>
+        <v>30.97842377071889</v>
       </c>
     </row>
     <row r="289">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>24.96236359708143</v>
+        <v>26.23924880389706</v>
       </c>
     </row>
   </sheetData>
